--- a/requerimientos/Catalogo_Requerimientos_Caso01_v2.4.xlsx
+++ b/requerimientos/Catalogo_Requerimientos_Caso01_v2.4.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Bases Técnicas del Caso 01, v1.0 · Consolidado de decisiones del numeral 16.1, v1.0 (documento de trabajo interno) · Subdocumento 3 — Esquema de solución y alcance, v1.4 · Registro de supuestos v1.4 · Registro de reglas de negocio v1.2 · Formulario T-12 v1.2, bloque A, como fuente de los requisitos transversales codificados</t>
+          <t>Bases Técnicas del Caso 01, v1.0 · Consolidado de decisiones del numeral 16.1, v1.0 (documento de trabajo interno) · Subdocumento 3 — Esquema de solución y alcance, v1.4 · Registro de supuestos v1.6 · Registro de reglas de negocio v1.2 · Formulario T-12 v1.2, bloque A, como fuente de los requisitos transversales codificados</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>1) RF-CAR-008 (prorrateo), RF-PES-006 (factor de corrección de pesaje) y RF-IDE-013 (biometría de portería) pasan a «Excluido del Contrato», conforme al apartado 3 del Subdocumento 3 v1.4, que los declara fuera de alcance en ambas etapas. RF-PES-006 estaba como Obligatorio con origen «diferido a Etapa 2». 2) RNF-DIS-010: se alinean origen primario y secundario con la matriz de trazabilidad, que los tenía invertidos. 3) Se cierran 11 estados «Por verificar» contrastando cada código citado contra el bloque A del Formulario T-12 v1.2: RF-IDE-014 (RT-06.20), RF-ADM-011 (RT-08.14), RNF-CAP-006, RNF-CAP-014, RNF-DIS-002, RNF-DIS-004, RNF-SEG-009, RNF-CUM-005, RNF-INF-003, RNF-MAN-005 y RNF-INT-003 (RT-05.20, no glosario). 4) RNF-DIS-005, RNF-MAN-006 y RNF-POR-003 siguen «Por verificar», pero su referencia pendiente es a las Bases Administrativas, no al documento transversal. 5) Se incorpora esta hoja: hasta la v2.4 el catálogo no declaraba versión, fecha ni control de cambios.</t>
+          <t>1) RF-CAR-008 (prorrateo), RF-PES-006 (factor de corrección de pesaje) y RF-IDE-013 (biometría de portería) pasan a «Excluido del Contrato», conforme al apartado 3 del Subdocumento 3 v1.4, que los declara fuera de alcance en ambas etapas. RF-PES-006 estaba como Obligatorio con origen «diferido a Etapa 2». 2) RNF-DIS-010: se alinean origen primario y secundario con la matriz de trazabilidad, que los tenía invertidos. 3) Se cierran 11 estados «Por verificar» contrastando cada código citado contra el bloque A del Formulario T-12 v1.2: RF-IDE-014 (RT-06.20), RF-ADM-011 (RT-08.14), RNF-CAP-006, RNF-CAP-014, RNF-DIS-002, RNF-DIS-004, RNF-SEG-009, RNF-CUM-005, RNF-INF-003, RNF-MAN-005 y RNF-INT-003 (RT-05.20, no glosario). 4) RNF-DIS-005, RNF-MAN-006 y RNF-POR-003 siguen «Por verificar», pero su referencia pendiente es a las Bases Administrativas, no al documento transversal. 5) Se incorpora esta hoja: hasta la v2.4 el catálogo no declaraba versión, fecha ni control de cambios. Revisión de consistencia del 4 de septiembre de 2026: se actualiza la versión citada del Registro de supuestos, hoy v1.6; la descripción de RF-AMB-014 y RF-AMB-015 se corrige en la matriz de trazabilidad, que la había abreviado, y no en este catálogo, que la trae completa.</t>
         </is>
       </c>
     </row>
